--- a/docs/downloads/13/tbl_repondant_alaotra_tous.xlsx
+++ b/docs/downloads/13/tbl_repondant_alaotra_tous.xlsx
@@ -382,9 +382,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +424,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -472,9 +466,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -547,9 +538,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -607,9 +595,6 @@
           <t>Code NA</t>
         </is>
       </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -667,9 +652,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -741,9 +723,6 @@
         <is>
           <t>Code NA</t>
         </is>
-      </c>
-      <c r="C26">
-        <v>2</v>
       </c>
     </row>
     <row r="27">

--- a/docs/downloads/13/tbl_repondant_alaotra_tous.xlsx
+++ b/docs/downloads/13/tbl_repondant_alaotra_tous.xlsx
@@ -374,7 +374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -386,7 +386,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -401,7 +401,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -416,7 +416,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -428,7 +428,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -443,7 +443,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -458,7 +458,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -500,7 +500,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -542,7 +542,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -557,7 +557,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -644,7 +644,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -656,7 +656,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -686,7 +686,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -728,7 +728,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
